--- a/skills/proposal-structure-generator/assets/checklist_public_partners.xlsx
+++ b/skills/proposal-structure-generator/assets/checklist_public_partners.xlsx
@@ -31,13 +31,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0052389D"/>
+      <color rgb="0051389D"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00919191"/>
+      <color rgb="00888888"/>
       <sz val="10"/>
     </font>
     <font>
@@ -66,7 +66,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0052389D"/>
+      <color rgb="0051389D"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -79,12 +79,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0052389D"/>
+        <fgColor rgb="0051389D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1EFFD"/>
+        <fgColor rgb="00F2EFFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -98,7 +98,7 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00F1EFFD"/>
+        <color rgb="00F2EFFE"/>
       </bottom>
     </border>
   </borders>
@@ -161,12 +161,12 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="0052389D"/>
+        <color rgb="0051389D"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="00919191"/>
+        <color rgb="00888888"/>
       </font>
     </dxf>
   </dxfs>

--- a/skills/proposal-structure-generator/assets/checklist_public_partners.xlsx
+++ b/skills/proposal-structure-generator/assets/checklist_public_partners.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Partners" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_notion" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Public Partners'!$A$4:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Public Partners'!$A$4:$H$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00374050"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
       <sz val="10"/>
     </font>
     <font>
@@ -115,7 +123,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,35 +132,39 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="3"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J82"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -540,10 +552,8 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="58" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Set Include to Yes or No (column E). Everything else is reference. See the Instructions tab.</t>
+          <t>Set Include to Yes or No (column E). Rows marked Always are fixed. See the Instructions tab.</t>
         </is>
       </c>
     </row>
@@ -593,20 +603,10 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Notion Block (Main Section &gt; Sub Section &gt; Section Title)</t>
+          <t>Build Result</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Notion Status</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Build Result</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -639,21 +639,11 @@
           <t>Fixed text</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I5" s="6">
-        <f>IF(E5="Always","Kept as in template",IF(E5="No","Omitted",IF(AND(C5="Body",H5="Reviewed"),"Notion text (no heading)",IF(C5="Body","Note: Subheader was empty.",IF(H5="Reviewed","Heading + Notion text"&amp;IF(F5="Table"," + template table",""),IF(H5="Not used","Heading"&amp;IF(F5="Table"," + template table",IF(F5="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F5="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="G5" s="6">
+        <f>IF(E5="No","Omitted",IF(C5="Fixed","Kept as in template",IF(AND(C5="Body",INDEX(_notion!$C$2:$C$66,MATCH(A5,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C5="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A5,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F5="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A5,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F5="Table"," + template table",IF(F5="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F5="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Template cover. Placeholders filled at build.</t>
         </is>
@@ -686,21 +676,11 @@
           <t>Fixed text</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I6" s="6">
-        <f>IF(E6="Always","Kept as in template",IF(E6="No","Omitted",IF(AND(C6="Body",H6="Reviewed"),"Notion text (no heading)",IF(C6="Body","Note: Subheader was empty.",IF(H6="Reviewed","Heading + Notion text"&amp;IF(F6="Table"," + template table",""),IF(H6="Not used","Heading"&amp;IF(F6="Table"," + template table",IF(F6="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F6="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="G6" s="6">
+        <f>IF(E6="No","Omitted",IF(C6="Fixed","Kept as in template",IF(AND(C6="Body",INDEX(_notion!$C$2:$C$66,MATCH(A6,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C6="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A6,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F6="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A6,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F6="Table"," + template table",IF(F6="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F6="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>TOC field, rebuilt from headings.</t>
         </is>
@@ -729,7 +709,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -737,21 +717,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Company Information</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I7" s="9">
-        <f>IF(E7="Always","Kept as in template",IF(E7="No","Omitted",IF(AND(C7="Body",H7="Reviewed"),"Notion text (no heading)",IF(C7="Body","Note: Subheader was empty.",IF(H7="Reviewed","Heading + Notion text"&amp;IF(F7="Table"," + template table",""),IF(H7="Not used","Heading"&amp;IF(F7="Table"," + template table",IF(F7="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F7="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="G7" s="9">
+        <f>IF(E7="No","Omitted",IF(C7="Fixed","Kept as in template",IF(AND(C7="Body",INDEX(_notion!$C$2:$C$66,MATCH(A7,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C7="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A7,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F7="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A7,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F7="Table"," + template table",IF(F7="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F7="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Template table already holds legal name, registration no., address. Notion block duplicates it and states 'Years Established: 2018'.</t>
         </is>
@@ -780,7 +750,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -788,23 +758,13 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I8" s="9">
-        <f>IF(E8="Always","Kept as in template",IF(E8="No","Omitted",IF(AND(C8="Body",H8="Reviewed"),"Notion text (no heading)",IF(C8="Body","Note: Subheader was empty.",IF(H8="Reviewed","Heading + Notion text"&amp;IF(F8="Table"," + template table",""),IF(H8="Not used","Heading"&amp;IF(F8="Table"," + template table",IF(F8="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F8="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>Consortium bids only.</t>
+      <c r="G8" s="9">
+        <f>IF(E8="No","Omitted",IF(C8="Fixed","Kept as in template",IF(AND(C8="Body",INDEX(_notion!$C$2:$C$66,MATCH(A8,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C8="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A8,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F8="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A8,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F8="Table"," + template table",IF(F8="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F8="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Template supplies the joint submission text and table.</t>
         </is>
       </c>
     </row>
@@ -831,7 +791,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -839,21 +799,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I9" s="9">
-        <f>IF(E9="Always","Kept as in template",IF(E9="No","Omitted",IF(AND(C9="Body",H9="Reviewed"),"Notion text (no heading)",IF(C9="Body","Note: Subheader was empty.",IF(H9="Reviewed","Heading + Notion text"&amp;IF(F9="Table"," + template table",""),IF(H9="Not used","Heading"&amp;IF(F9="Table"," + template table",IF(F9="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F9="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="G9" s="9">
+        <f>IF(E9="No","Omitted",IF(C9="Fixed","Kept as in template",IF(AND(C9="Body",INDEX(_notion!$C$2:$C$66,MATCH(A9,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C9="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A9,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F9="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A9,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F9="Table"," + template table",IF(F9="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F9="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Writing guide: every proposal. Tender-specific.</t>
         </is>
@@ -882,7 +832,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -890,21 +840,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Compliance and Eligibility</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I10" s="9">
-        <f>IF(E10="Always","Kept as in template",IF(E10="No","Omitted",IF(AND(C10="Body",H10="Reviewed"),"Notion text (no heading)",IF(C10="Body","Note: Subheader was empty.",IF(H10="Reviewed","Heading + Notion text"&amp;IF(F10="Table"," + template table",""),IF(H10="Not used","Heading"&amp;IF(F10="Table"," + template table",IF(F10="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F10="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
+      <c r="G10" s="9">
+        <f>IF(E10="No","Omitted",IF(C10="Fixed","Kept as in template",IF(AND(C10="Body",INDEX(_notion!$C$2:$C$66,MATCH(A10,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C10="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A10,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F10="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A10,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F10="Table"," + template table",IF(F10="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F10="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Notion block holds the same annex list as the template table.</t>
         </is>
@@ -933,7 +873,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -941,21 +881,11 @@
           <t>Replaced</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I11" s="9">
-        <f>IF(E11="Always","Kept as in template",IF(E11="No","Omitted",IF(AND(C11="Body",H11="Reviewed"),"Notion text (no heading)",IF(C11="Body","Note: Subheader was empty.",IF(H11="Reviewed","Heading + Notion text"&amp;IF(F11="Table"," + template table",""),IF(H11="Not used","Heading"&amp;IF(F11="Table"," + template table",IF(F11="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F11="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
+      <c r="G11" s="9">
+        <f>IF(E11="No","Omitted",IF(C11="Fixed","Kept as in template",IF(AND(C11="Body",INDEX(_notion!$C$2:$C$66,MATCH(A11,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C11="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A11,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F11="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A11,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F11="Table"," + template table",IF(F11="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F11="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Template text is identical to the three Notion blocks below and is replaced by them.</t>
         </is>
@@ -978,9 +908,9 @@
           <t>About Start2 Group</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Always</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -988,21 +918,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>Company Overview &gt; About Start2 Group</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I12" s="13">
-        <f>IF(E12="Always","Kept as in template",IF(E12="No","Omitted",IF(AND(C12="Body",H12="Reviewed"),"Notion text (no heading)",IF(C12="Body","Note: Subheader was empty.",IF(H12="Reviewed","Heading + Notion text"&amp;IF(F12="Table"," + template table",""),IF(H12="Not used","Heading"&amp;IF(F12="Table"," + template table",IF(F12="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F12="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="G12" s="12">
+        <f>IF(E12="No","Omitted",IF(C12="Fixed","Kept as in template",IF(AND(C12="Body",INDEX(_notion!$C$2:$C$66,MATCH(A12,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C12="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A12,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F12="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A12,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F12="Table"," + template table",IF(F12="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F12="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Body text, no heading.</t>
         </is>
@@ -1025,9 +945,9 @@
           <t>Geographical Presence</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Always</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -1035,21 +955,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>Company Overview &gt; About Start2 Group &gt; Geographical Presence</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I13" s="13">
-        <f>IF(E13="Always","Kept as in template",IF(E13="No","Omitted",IF(AND(C13="Body",H13="Reviewed"),"Notion text (no heading)",IF(C13="Body","Note: Subheader was empty.",IF(H13="Reviewed","Heading + Notion text"&amp;IF(F13="Table"," + template table",""),IF(H13="Not used","Heading"&amp;IF(F13="Table"," + template table",IF(F13="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F13="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="G13" s="12">
+        <f>IF(E13="No","Omitted",IF(C13="Fixed","Kept as in template",IF(AND(C13="Body",INDEX(_notion!$C$2:$C$66,MATCH(A13,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C13="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A13,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F13="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A13,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F13="Table"," + template table",IF(F13="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F13="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Body text, no heading.</t>
         </is>
@@ -1072,9 +982,9 @@
           <t>Key Benefits of Partnering with Start2 Group</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Always</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -1082,21 +992,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>Company Overview &gt; Key Benefits of Partnering with Start2 Group</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I14" s="13">
-        <f>IF(E14="Always","Kept as in template",IF(E14="No","Omitted",IF(AND(C14="Body",H14="Reviewed"),"Notion text (no heading)",IF(C14="Body","Note: Subheader was empty.",IF(H14="Reviewed","Heading + Notion text"&amp;IF(F14="Table"," + template table",""),IF(H14="Not used","Heading"&amp;IF(F14="Table"," + template table",IF(F14="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F14="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
+      <c r="G14" s="12">
+        <f>IF(E14="No","Omitted",IF(C14="Fixed","Kept as in template",IF(AND(C14="Body",INDEX(_notion!$C$2:$C$66,MATCH(A14,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C14="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A14,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F14="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A14,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F14="Table"," + template table",IF(F14="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F14="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Body text, no heading.</t>
         </is>
@@ -1123,7 +1023,7 @@
           <t>Relevant Expertise of the Firm</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1133,21 +1033,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I15" s="9">
-        <f>IF(E15="Always","Kept as in template",IF(E15="No","Omitted",IF(AND(C15="Body",H15="Reviewed"),"Notion text (no heading)",IF(C15="Body","Note: Subheader was empty.",IF(H15="Reviewed","Heading + Notion text"&amp;IF(F15="Table"," + template table",""),IF(H15="Not used","Heading"&amp;IF(F15="Table"," + template table",IF(F15="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F15="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J15" s="9" t="inlineStr"/>
+      <c r="G15" s="9">
+        <f>IF(E15="No","Omitted",IF(C15="Fixed","Kept as in template",IF(AND(C15="Body",INDEX(_notion!$C$2:$C$66,MATCH(A15,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C15="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A15,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F15="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A15,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F15="Table"," + template table",IF(F15="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F15="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1170,7 +1060,7 @@
           <t>Experience in Startup Acceleration</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1180,21 +1070,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in High Tech Acceleration Programs</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I16" s="6">
-        <f>IF(E16="Always","Kept as in template",IF(E16="No","Omitted",IF(AND(C16="Body",H16="Reviewed"),"Notion text (no heading)",IF(C16="Body","Note: Subheader was empty.",IF(H16="Reviewed","Heading + Notion text"&amp;IF(F16="Table"," + template table",""),IF(H16="Not used","Heading"&amp;IF(F16="Table"," + template table",IF(F16="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F16="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="G16" s="6">
+        <f>IF(E16="No","Omitted",IF(C16="Fixed","Kept as in template",IF(AND(C16="Body",INDEX(_notion!$C$2:$C$66,MATCH(A16,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C16="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A16,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F16="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A16,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F16="Table"," + template table",IF(F16="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F16="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>Template table is the 6,000+ stat strip.</t>
         </is>
@@ -1221,7 +1101,7 @@
           <t>Experience in Geographies</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1231,21 +1111,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I17" s="6">
-        <f>IF(E17="Always","Kept as in template",IF(E17="No","Omitted",IF(AND(C17="Body",H17="Reviewed"),"Notion text (no heading)",IF(C17="Body","Note: Subheader was empty.",IF(H17="Reviewed","Heading + Notion text"&amp;IF(F17="Table"," + template table",""),IF(H17="Not used","Heading"&amp;IF(F17="Table"," + template table",IF(F17="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F17="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="G17" s="6">
+        <f>IF(E17="No","Omitted",IF(C17="Fixed","Kept as in template",IF(AND(C17="Body",INDEX(_notion!$C$2:$C$66,MATCH(A17,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C17="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A17,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F17="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A17,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F17="Table"," + template table",IF(F17="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F17="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Parent of regional subheads.</t>
         </is>
@@ -1267,12 +1137,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Asia</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1282,21 +1152,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Asia</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I18" s="6">
-        <f>IF(E18="Always","Kept as in template",IF(E18="No","Omitted",IF(AND(C18="Body",H18="Reviewed"),"Notion text (no heading)",IF(C18="Body","Note: Subheader was empty.",IF(H18="Reviewed","Heading + Notion text"&amp;IF(F18="Table"," + template table",""),IF(H18="Not used","Heading"&amp;IF(F18="Table"," + template table",IF(F18="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F18="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
+      <c r="G18" s="6">
+        <f>IF(E18="No","Omitted",IF(C18="Fixed","Kept as in template",IF(AND(C18="Body",INDEX(_notion!$C$2:$C$66,MATCH(A18,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C18="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A18,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F18="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A18,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F18="Table"," + template table",IF(F18="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F18="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1314,12 +1174,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1329,21 +1189,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Europe</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I19" s="6">
-        <f>IF(E19="Always","Kept as in template",IF(E19="No","Omitted",IF(AND(C19="Body",H19="Reviewed"),"Notion text (no heading)",IF(C19="Body","Note: Subheader was empty.",IF(H19="Reviewed","Heading + Notion text"&amp;IF(F19="Table"," + template table",""),IF(H19="Not used","Heading"&amp;IF(F19="Table"," + template table",IF(F19="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F19="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
+      <c r="G19" s="6">
+        <f>IF(E19="No","Omitted",IF(C19="Fixed","Kept as in template",IF(AND(C19="Body",INDEX(_notion!$C$2:$C$66,MATCH(A19,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C19="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A19,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F19="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A19,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F19="Table"," + template table",IF(F19="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F19="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1361,12 +1211,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Americas</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1376,21 +1226,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Americas</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I20" s="6">
-        <f>IF(E20="Always","Kept as in template",IF(E20="No","Omitted",IF(AND(C20="Body",H20="Reviewed"),"Notion text (no heading)",IF(C20="Body","Note: Subheader was empty.",IF(H20="Reviewed","Heading + Notion text"&amp;IF(F20="Table"," + template table",""),IF(H20="Not used","Heading"&amp;IF(F20="Table"," + template table",IF(F20="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F20="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="G20" s="6">
+        <f>IF(E20="No","Omitted",IF(C20="Fixed","Kept as in template",IF(AND(C20="Body",INDEX(_notion!$C$2:$C$66,MATCH(A20,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C20="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A20,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F20="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A20,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F20="Table"," + template table",IF(F20="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F20="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Old checklist called this North America.</t>
         </is>
@@ -1417,7 +1257,7 @@
           <t>Experience in Verticals</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1427,21 +1267,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I21" s="6">
-        <f>IF(E21="Always","Kept as in template",IF(E21="No","Omitted",IF(AND(C21="Body",H21="Reviewed"),"Notion text (no heading)",IF(C21="Body","Note: Subheader was empty.",IF(H21="Reviewed","Heading + Notion text"&amp;IF(F21="Table"," + template table",""),IF(H21="Not used","Heading"&amp;IF(F21="Table"," + template table",IF(F21="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F21="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="G21" s="6">
+        <f>IF(E21="No","Omitted",IF(C21="Fixed","Kept as in template",IF(AND(C21="Body",INDEX(_notion!$C$2:$C$66,MATCH(A21,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C21="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A21,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F21="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A21,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F21="Table"," + template table",IF(F21="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F21="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>Parent of vertical subheads.</t>
         </is>
@@ -1463,12 +1293,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Climate Technology</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1478,21 +1308,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Climate Technology</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I22" s="6">
-        <f>IF(E22="Always","Kept as in template",IF(E22="No","Omitted",IF(AND(C22="Body",H22="Reviewed"),"Notion text (no heading)",IF(C22="Body","Note: Subheader was empty.",IF(H22="Reviewed","Heading + Notion text"&amp;IF(F22="Table"," + template table",""),IF(H22="Not used","Heading"&amp;IF(F22="Table"," + template table",IF(F22="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F22="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="G22" s="6">
+        <f>IF(E22="No","Omitted",IF(C22="Fixed","Kept as in template",IF(AND(C22="Body",INDEX(_notion!$C$2:$C$66,MATCH(A22,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C22="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A22,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F22="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A22,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F22="Table"," + template table",IF(F22="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F22="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Covers Greentech and agrifood tech.</t>
         </is>
@@ -1514,12 +1334,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1529,21 +1349,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Manufacturing</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I23" s="6">
-        <f>IF(E23="Always","Kept as in template",IF(E23="No","Omitted",IF(AND(C23="Body",H23="Reviewed"),"Notion text (no heading)",IF(C23="Body","Note: Subheader was empty.",IF(H23="Reviewed","Heading + Notion text"&amp;IF(F23="Table"," + template table",""),IF(H23="Not used","Heading"&amp;IF(F23="Table"," + template table",IF(F23="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F23="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J23" s="6" t="inlineStr"/>
+      <c r="G23" s="6">
+        <f>IF(E23="No","Omitted",IF(C23="Fixed","Kept as in template",IF(AND(C23="Body",INDEX(_notion!$C$2:$C$66,MATCH(A23,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C23="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A23,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F23="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A23,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F23="Table"," + template table",IF(F23="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F23="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1561,12 +1371,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1576,21 +1386,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Automotive</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I24" s="6">
-        <f>IF(E24="Always","Kept as in template",IF(E24="No","Omitted",IF(AND(C24="Body",H24="Reviewed"),"Notion text (no heading)",IF(C24="Body","Note: Subheader was empty.",IF(H24="Reviewed","Heading + Notion text"&amp;IF(F24="Table"," + template table",""),IF(H24="Not used","Heading"&amp;IF(F24="Table"," + template table",IF(F24="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F24="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J24" s="6" t="inlineStr"/>
+      <c r="G24" s="6">
+        <f>IF(E24="No","Omitted",IF(C24="Fixed","Kept as in template",IF(AND(C24="Body",INDEX(_notion!$C$2:$C$66,MATCH(A24,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C24="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A24,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F24="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A24,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F24="Table"," + template table",IF(F24="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F24="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1608,12 +1408,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>Fintech</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1623,21 +1423,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I25" s="6">
-        <f>IF(E25="Always","Kept as in template",IF(E25="No","Omitted",IF(AND(C25="Body",H25="Reviewed"),"Notion text (no heading)",IF(C25="Body","Note: Subheader was empty.",IF(H25="Reviewed","Heading + Notion text"&amp;IF(F25="Table"," + template table",""),IF(H25="Not used","Heading"&amp;IF(F25="Table"," + template table",IF(F25="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F25="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="G25" s="6">
+        <f>IF(E25="No","Omitted",IF(C25="Fixed","Kept as in template",IF(AND(C25="Body",INDEX(_notion!$C$2:$C$66,MATCH(A25,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C25="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A25,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F25="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A25,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F25="Table"," + template table",IF(F25="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F25="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>From old checklist.</t>
         </is>
@@ -1659,12 +1449,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Digital Health / Healthcare</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1674,21 +1464,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I26" s="6">
-        <f>IF(E26="Always","Kept as in template",IF(E26="No","Omitted",IF(AND(C26="Body",H26="Reviewed"),"Notion text (no heading)",IF(C26="Body","Note: Subheader was empty.",IF(H26="Reviewed","Heading + Notion text"&amp;IF(F26="Table"," + template table",""),IF(H26="Not used","Heading"&amp;IF(F26="Table"," + template table",IF(F26="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F26="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="G26" s="6">
+        <f>IF(E26="No","Omitted",IF(C26="Fixed","Kept as in template",IF(AND(C26="Body",INDEX(_notion!$C$2:$C$66,MATCH(A26,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C26="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A26,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F26="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A26,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F26="Table"," + template table",IF(F26="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F26="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>From old checklist.</t>
         </is>
@@ -1710,12 +1490,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>Foodtech</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1725,21 +1505,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I27" s="6">
-        <f>IF(E27="Always","Kept as in template",IF(E27="No","Omitted",IF(AND(C27="Body",H27="Reviewed"),"Notion text (no heading)",IF(C27="Body","Note: Subheader was empty.",IF(H27="Reviewed","Heading + Notion text"&amp;IF(F27="Table"," + template table",""),IF(H27="Not used","Heading"&amp;IF(F27="Table"," + template table",IF(F27="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F27="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
+      <c r="G27" s="6">
+        <f>IF(E27="No","Omitted",IF(C27="Fixed","Kept as in template",IF(AND(C27="Body",INDEX(_notion!$C$2:$C$66,MATCH(A27,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C27="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A27,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F27="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A27,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F27="Table"," + template table",IF(F27="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F27="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>From old checklist. Climate Technology mentions agrifood tech.</t>
         </is>
@@ -1761,12 +1531,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1776,21 +1546,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I28" s="6">
-        <f>IF(E28="Always","Kept as in template",IF(E28="No","Omitted",IF(AND(C28="Body",H28="Reviewed"),"Notion text (no heading)",IF(C28="Body","Note: Subheader was empty.",IF(H28="Reviewed","Heading + Notion text"&amp;IF(F28="Table"," + template table",""),IF(H28="Not used","Heading"&amp;IF(F28="Table"," + template table",IF(F28="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F28="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="G28" s="6">
+        <f>IF(E28="No","Omitted",IF(C28="Fixed","Kept as in template",IF(AND(C28="Body",INDEX(_notion!$C$2:$C$66,MATCH(A28,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C28="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A28,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F28="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A28,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F28="Table"," + template table",IF(F28="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F28="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>From old checklist.</t>
         </is>
@@ -1817,7 +1577,7 @@
           <t>Experience in Technology Focus</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1827,21 +1587,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I29" s="6">
-        <f>IF(E29="Always","Kept as in template",IF(E29="No","Omitted",IF(AND(C29="Body",H29="Reviewed"),"Notion text (no heading)",IF(C29="Body","Note: Subheader was empty.",IF(H29="Reviewed","Heading + Notion text"&amp;IF(F29="Table"," + template table",""),IF(H29="Not used","Heading"&amp;IF(F29="Table"," + template table",IF(F29="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F29="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="G29" s="6">
+        <f>IF(E29="No","Omitted",IF(C29="Fixed","Kept as in template",IF(AND(C29="Body",INDEX(_notion!$C$2:$C$66,MATCH(A29,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C29="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A29,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F29="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A29,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F29="Table"," + template table",IF(F29="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F29="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>Parent of technology subheads.</t>
         </is>
@@ -1863,12 +1613,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1878,21 +1628,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Technology Focus &gt; Artificial Intelligence</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I30" s="6">
-        <f>IF(E30="Always","Kept as in template",IF(E30="No","Omitted",IF(AND(C30="Body",H30="Reviewed"),"Notion text (no heading)",IF(C30="Body","Note: Subheader was empty.",IF(H30="Reviewed","Heading + Notion text"&amp;IF(F30="Table"," + template table",""),IF(H30="Not used","Heading"&amp;IF(F30="Table"," + template table",IF(F30="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F30="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J30" s="6" t="inlineStr"/>
+      <c r="G30" s="6">
+        <f>IF(E30="No","Omitted",IF(C30="Fixed","Kept as in template",IF(AND(C30="Body",INDEX(_notion!$C$2:$C$66,MATCH(A30,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C30="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A30,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F30="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A30,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F30="Table"," + template table",IF(F30="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F30="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1910,12 +1650,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>Deep Tech</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1925,21 +1665,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Experience in Technology Focus &gt; Deep Tech</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I31" s="6">
-        <f>IF(E31="Always","Kept as in template",IF(E31="No","Omitted",IF(AND(C31="Body",H31="Reviewed"),"Notion text (no heading)",IF(C31="Body","Note: Subheader was empty.",IF(H31="Reviewed","Heading + Notion text"&amp;IF(F31="Table"," + template table",""),IF(H31="Not used","Heading"&amp;IF(F31="Table"," + template table",IF(F31="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F31="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J31" s="6" t="inlineStr"/>
+      <c r="G31" s="6">
+        <f>IF(E31="No","Omitted",IF(C31="Fixed","Kept as in template",IF(AND(C31="Body",INDEX(_notion!$C$2:$C$66,MATCH(A31,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C31="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A31,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F31="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A31,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F31="Table"," + template table",IF(F31="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F31="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1962,7 +1692,7 @@
           <t>Our Mentor Network</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1972,21 +1702,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Information on Network &gt; Our Mentor Network</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I32" s="6">
-        <f>IF(E32="Always","Kept as in template",IF(E32="No","Omitted",IF(AND(C32="Body",H32="Reviewed"),"Notion text (no heading)",IF(C32="Body","Note: Subheader was empty.",IF(H32="Reviewed","Heading + Notion text"&amp;IF(F32="Table"," + template table",""),IF(H32="Not used","Heading"&amp;IF(F32="Table"," + template table",IF(F32="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F32="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J32" s="6" t="inlineStr"/>
+      <c r="G32" s="6">
+        <f>IF(E32="No","Omitted",IF(C32="Fixed","Kept as in template",IF(AND(C32="Body",INDEX(_notion!$C$2:$C$66,MATCH(A32,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C32="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A32,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F32="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A32,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F32="Table"," + template table",IF(F32="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F32="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2009,7 +1729,7 @@
           <t>Our Investor Network</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2019,21 +1739,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Information on Network &gt; Our Investor Network</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I33" s="6">
-        <f>IF(E33="Always","Kept as in template",IF(E33="No","Omitted",IF(AND(C33="Body",H33="Reviewed"),"Notion text (no heading)",IF(C33="Body","Note: Subheader was empty.",IF(H33="Reviewed","Heading + Notion text"&amp;IF(F33="Table"," + template table",""),IF(H33="Not used","Heading"&amp;IF(F33="Table"," + template table",IF(F33="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F33="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J33" s="6" t="inlineStr"/>
+      <c r="G33" s="6">
+        <f>IF(E33="No","Omitted",IF(C33="Fixed","Kept as in template",IF(AND(C33="Body",INDEX(_notion!$C$2:$C$66,MATCH(A33,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C33="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A33,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F33="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A33,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F33="Table"," + template table",IF(F33="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F33="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2056,7 +1766,7 @@
           <t>Our Partner Network</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2066,21 +1776,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Expertise of the Firm &gt; Information on Network &gt; Our Partner Network</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I34" s="6">
-        <f>IF(E34="Always","Kept as in template",IF(E34="No","Omitted",IF(AND(C34="Body",H34="Reviewed"),"Notion text (no heading)",IF(C34="Body","Note: Subheader was empty.",IF(H34="Reviewed","Heading + Notion text"&amp;IF(F34="Table"," + template table",""),IF(H34="Not used","Heading"&amp;IF(F34="Table"," + template table",IF(F34="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F34="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J34" s="6" t="inlineStr"/>
+      <c r="G34" s="6">
+        <f>IF(E34="No","Omitted",IF(C34="Fixed","Kept as in template",IF(AND(C34="Body",INDEX(_notion!$C$2:$C$66,MATCH(A34,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C34="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A34,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F34="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A34,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F34="Table"," + template table",IF(F34="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F34="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -2103,7 +1803,7 @@
           <t>Relevant Program Track Record</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2113,21 +1813,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I35" s="9">
-        <f>IF(E35="Always","Kept as in template",IF(E35="No","Omitted",IF(AND(C35="Body",H35="Reviewed"),"Notion text (no heading)",IF(C35="Body","Note: Subheader was empty.",IF(H35="Reviewed","Heading + Notion text"&amp;IF(F35="Table"," + template table",""),IF(H35="Not used","Heading"&amp;IF(F35="Table"," + template table",IF(F35="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F35="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J35" s="9" t="inlineStr"/>
+      <c r="G35" s="9">
+        <f>IF(E35="No","Omitted",IF(C35="Fixed","Kept as in template",IF(AND(C35="Body",INDEX(_notion!$C$2:$C$66,MATCH(A35,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C35="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A35,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F35="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A35,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F35="Table"," + template table",IF(F35="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F35="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2150,7 +1840,7 @@
           <t>Program Track Record</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2160,21 +1850,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Relevant Track Record &gt; Program Track Record</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I36" s="6">
-        <f>IF(E36="Always","Kept as in template",IF(E36="No","Omitted",IF(AND(C36="Body",H36="Reviewed"),"Notion text (no heading)",IF(C36="Body","Note: Subheader was empty.",IF(H36="Reviewed","Heading + Notion text"&amp;IF(F36="Table"," + template table",""),IF(H36="Not used","Heading"&amp;IF(F36="Table"," + template table",IF(F36="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F36="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
+      <c r="G36" s="6">
+        <f>IF(E36="No","Omitted",IF(C36="Fixed","Kept as in template",IF(AND(C36="Body",INDEX(_notion!$C$2:$C$66,MATCH(A36,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C36="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A36,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F36="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A36,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F36="Table"," + template table",IF(F36="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F36="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Template table: Logo / Client / Scope / Value.</t>
         </is>
@@ -2201,7 +1881,7 @@
           <t>Startup Success Stories</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2211,21 +1891,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Relevant Track Record &gt; Startup Success Stories</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I37" s="6">
-        <f>IF(E37="Always","Kept as in template",IF(E37="No","Omitted",IF(AND(C37="Body",H37="Reviewed"),"Notion text (no heading)",IF(C37="Body","Note: Subheader was empty.",IF(H37="Reviewed","Heading + Notion text"&amp;IF(F37="Table"," + template table",""),IF(H37="Not used","Heading"&amp;IF(F37="Table"," + template table",IF(F37="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F37="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="G37" s="6">
+        <f>IF(E37="No","Omitted",IF(C37="Fixed","Kept as in template",IF(AND(C37="Body",INDEX(_notion!$C$2:$C$66,MATCH(A37,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C37="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A37,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F37="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A37,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F37="Table"," + template table",IF(F37="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F37="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Notion remark: connect to Startup Success Stories database.</t>
         </is>
@@ -2247,12 +1917,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Our Fundraising Support to Startups</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2262,21 +1932,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Relevant Track Record &gt; Startup Success Stories &gt; Our Fundraising Support to Startups</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I38" s="6">
-        <f>IF(E38="Always","Kept as in template",IF(E38="No","Omitted",IF(AND(C38="Body",H38="Reviewed"),"Notion text (no heading)",IF(C38="Body","Note: Subheader was empty.",IF(H38="Reviewed","Heading + Notion text"&amp;IF(F38="Table"," + template table",""),IF(H38="Not used","Heading"&amp;IF(F38="Table"," + template table",IF(F38="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F38="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J38" s="6" t="inlineStr"/>
+      <c r="G38" s="6">
+        <f>IF(E38="No","Omitted",IF(C38="Fixed","Kept as in template",IF(AND(C38="Body",INDEX(_notion!$C$2:$C$66,MATCH(A38,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C38="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A38,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F38="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A38,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F38="Table"," + template table",IF(F38="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F38="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2299,7 +1959,7 @@
           <t>Trade Mission Success Stories</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2309,21 +1969,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I39" s="6">
-        <f>IF(E39="Always","Kept as in template",IF(E39="No","Omitted",IF(AND(C39="Body",H39="Reviewed"),"Notion text (no heading)",IF(C39="Body","Note: Subheader was empty.",IF(H39="Reviewed","Heading + Notion text"&amp;IF(F39="Table"," + template table",""),IF(H39="Not used","Heading"&amp;IF(F39="Table"," + template table",IF(F39="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F39="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="G39" s="6">
+        <f>IF(E39="No","Omitted",IF(C39="Fixed","Kept as in template",IF(AND(C39="Body",INDEX(_notion!$C$2:$C$66,MATCH(A39,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C39="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A39,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F39="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A39,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F39="Table"," + template table",IF(F39="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F39="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>Not in template. From old checklist.</t>
         </is>
@@ -2350,7 +2000,7 @@
           <t>Program Structure</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2360,21 +2010,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I40" s="9">
-        <f>IF(E40="Always","Kept as in template",IF(E40="No","Omitted",IF(AND(C40="Body",H40="Reviewed"),"Notion text (no heading)",IF(C40="Body","Note: Subheader was empty.",IF(H40="Reviewed","Heading + Notion text"&amp;IF(F40="Table"," + template table",""),IF(H40="Not used","Heading"&amp;IF(F40="Table"," + template table",IF(F40="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F40="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
+      <c r="G40" s="9">
+        <f>IF(E40="No","Omitted",IF(C40="Fixed","Kept as in template",IF(AND(C40="Body",INDEX(_notion!$C$2:$C$66,MATCH(A40,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C40="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A40,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F40="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A40,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F40="Table"," + template table",IF(F40="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F40="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
         <is>
           <t>Writing guide: nearly all proposals.</t>
         </is>
@@ -2401,7 +2041,7 @@
           <t>Methodology and Frameworks for Success</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2411,21 +2051,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I41" s="6">
-        <f>IF(E41="Always","Kept as in template",IF(E41="No","Omitted",IF(AND(C41="Body",H41="Reviewed"),"Notion text (no heading)",IF(C41="Body","Note: Subheader was empty.",IF(H41="Reviewed","Heading + Notion text"&amp;IF(F41="Table"," + template table",""),IF(H41="Not used","Heading"&amp;IF(F41="Table"," + template table",IF(F41="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F41="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J41" s="6" t="inlineStr"/>
+      <c r="G41" s="6">
+        <f>IF(E41="No","Omitted",IF(C41="Fixed","Kept as in template",IF(AND(C41="Body",INDEX(_notion!$C$2:$C$66,MATCH(A41,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C41="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A41,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F41="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A41,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F41="Table"," + template table",IF(F41="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F41="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -2443,12 +2073,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D42" s="16" t="inlineStr">
         <is>
           <t>Program Design Strategy and Methodology</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2458,21 +2088,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Program Structure &gt; Methodology and Frameworks for Success &gt; Program Design Strategy and Methodology</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Pending Review</t>
-        </is>
-      </c>
-      <c r="I42" s="6">
-        <f>IF(E42="Always","Kept as in template",IF(E42="No","Omitted",IF(AND(C42="Body",H42="Reviewed"),"Notion text (no heading)",IF(C42="Body","Note: Subheader was empty.",IF(H42="Reviewed","Heading + Notion text"&amp;IF(F42="Table"," + template table",""),IF(H42="Not used","Heading"&amp;IF(F42="Table"," + template table",IF(F42="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F42="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="G42" s="6">
+        <f>IF(E42="No","Omitted",IF(C42="Fixed","Kept as in template",IF(AND(C42="Body",INDEX(_notion!$C$2:$C$66,MATCH(A42,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C42="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A42,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F42="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A42,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F42="Table"," + template table",IF(F42="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F42="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Notion text exists but is Pending Review, so it is not inserted.</t>
         </is>
@@ -2494,12 +2114,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>Recruitment and Selection Strategy</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2509,21 +2129,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Program Structure &gt; Methodology and Frameworks for Success &gt; Recruitment &amp; Selection Strategy</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I43" s="6">
-        <f>IF(E43="Always","Kept as in template",IF(E43="No","Omitted",IF(AND(C43="Body",H43="Reviewed"),"Notion text (no heading)",IF(C43="Body","Note: Subheader was empty.",IF(H43="Reviewed","Heading + Notion text"&amp;IF(F43="Table"," + template table",""),IF(H43="Not used","Heading"&amp;IF(F43="Table"," + template table",IF(F43="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F43="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
+      <c r="G43" s="6">
+        <f>IF(E43="No","Omitted",IF(C43="Fixed","Kept as in template",IF(AND(C43="Body",INDEX(_notion!$C$2:$C$66,MATCH(A43,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C43="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A43,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F43="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A43,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F43="Table"," + template table",IF(F43="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F43="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Covers marketing, prospecting and screening.</t>
         </is>
@@ -2550,7 +2160,7 @@
           <t>Program Components</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2560,21 +2170,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I44" s="6">
-        <f>IF(E44="Always","Kept as in template",IF(E44="No","Omitted",IF(AND(C44="Body",H44="Reviewed"),"Notion text (no heading)",IF(C44="Body","Note: Subheader was empty.",IF(H44="Reviewed","Heading + Notion text"&amp;IF(F44="Table"," + template table",""),IF(H44="Not used","Heading"&amp;IF(F44="Table"," + template table",IF(F44="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F44="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J44" s="6" t="inlineStr"/>
+      <c r="G44" s="6">
+        <f>IF(E44="No","Omitted",IF(C44="Fixed","Kept as in template",IF(AND(C44="Body",INDEX(_notion!$C$2:$C$66,MATCH(A44,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C44="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A44,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F44="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A44,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F44="Table"," + template table",IF(F44="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F44="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -2592,12 +2192,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>Delivery Approach</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2607,21 +2207,11 @@
           <t>Placeholder</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I45" s="6">
-        <f>IF(E45="Always","Kept as in template",IF(E45="No","Omitted",IF(AND(C45="Body",H45="Reviewed"),"Notion text (no heading)",IF(C45="Body","Note: Subheader was empty.",IF(H45="Reviewed","Heading + Notion text"&amp;IF(F45="Table"," + template table",""),IF(H45="Not used","Heading"&amp;IF(F45="Table"," + template table",IF(F45="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F45="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J45" s="6" t="inlineStr"/>
+      <c r="G45" s="6">
+        <f>IF(E45="No","Omitted",IF(C45="Fixed","Kept as in template",IF(AND(C45="Body",INDEX(_notion!$C$2:$C$66,MATCH(A45,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C45="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A45,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F45="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A45,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F45="Table"," + template table",IF(F45="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F45="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -2639,12 +2229,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D46" s="16" t="inlineStr">
         <is>
           <t>Workplan and Time Table</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="E46" s="15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2654,21 +2244,11 @@
           <t>Table</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I46" s="6">
-        <f>IF(E46="Always","Kept as in template",IF(E46="No","Omitted",IF(AND(C46="Body",H46="Reviewed"),"Notion text (no heading)",IF(C46="Body","Note: Subheader was empty.",IF(H46="Reviewed","Heading + Notion text"&amp;IF(F46="Table"," + template table",""),IF(H46="Not used","Heading"&amp;IF(F46="Table"," + template table",IF(F46="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F46="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J46" s="6" t="inlineStr"/>
+      <c r="G46" s="6">
+        <f>IF(E46="No","Omitted",IF(C46="Fixed","Kept as in template",IF(AND(C46="Body",INDEX(_notion!$C$2:$C$66,MATCH(A46,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C46="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A46,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F46="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A46,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F46="Table"," + template table",IF(F46="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F46="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -2686,12 +2266,12 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Online Components</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2701,21 +2281,11 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I47" s="6">
-        <f>IF(E47="Always","Kept as in template",IF(E47="No","Omitted",IF(AND(C47="Body",H47="Reviewed"),"Notion text (no heading)",IF(C47="Body","Note: Subheader was empty.",IF(H47="Reviewed","Heading + Notion text"&amp;IF(F47="Table"," + template table",""),IF(H47="Not used","Heading"&amp;IF(F47="Table"," + template table",IF(F47="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F47="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="G47" s="6">
+        <f>IF(E47="No","Omitted",IF(C47="Fixed","Kept as in template",IF(AND(C47="Body",INDEX(_notion!$C$2:$C$66,MATCH(A47,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C47="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A47,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F47="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A47,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F47="Table"," + template table",IF(F47="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F47="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
         <is>
           <t>Parent of online subheads.</t>
         </is>
@@ -2724,25 +2294,25 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>PP-044</t>
+          <t>PP-051</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.1</t>
+          <t>8.2.4</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
+          <t>Offline Components</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2752,48 +2322,38 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I48" s="6">
-        <f>IF(E48="Always","Kept as in template",IF(E48="No","Omitted",IF(AND(C48="Body",H48="Reviewed"),"Notion text (no heading)",IF(C48="Body","Note: Subheader was empty.",IF(H48="Reviewed","Heading + Notion text"&amp;IF(F48="Table"," + template table",""),IF(H48="Not used","Heading"&amp;IF(F48="Table"," + template table",IF(F48="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F48="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>Program Design block describes workshops (Pending Review).</t>
+      <c r="G48" s="6">
+        <f>IF(E48="No","Omitted",IF(C48="Fixed","Kept as in template",IF(AND(C48="Body",INDEX(_notion!$C$2:$C$66,MATCH(A48,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C48="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A48,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F48="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A48,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F48="Table"," + template table",IF(F48="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F48="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Parent of offline subheads.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>PP-045</t>
+          <t>PP-058</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.2</t>
+          <t>8.2.5</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Mentoring</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
+          <t>Open Innovation / Hackathon Management</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2803,46 +2363,40 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I49" s="6">
-        <f>IF(E49="Always","Kept as in template",IF(E49="No","Omitted",IF(AND(C49="Body",H49="Reviewed"),"Notion text (no heading)",IF(C49="Body","Note: Subheader was empty.",IF(H49="Reviewed","Heading + Notion text"&amp;IF(F49="Table"," + template table",""),IF(H49="Not used","Heading"&amp;IF(F49="Table"," + template table",IF(F49="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F49="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J49" s="6" t="inlineStr"/>
+      <c r="G49" s="6">
+        <f>IF(E49="No","Omitted",IF(C49="Fixed","Kept as in template",IF(AND(C49="Body",INDEX(_notion!$C$2:$C$66,MATCH(A49,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C49="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A49,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F49="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A49,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F49="Table"," + template table",IF(F49="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F49="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Not in template. From old checklist.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>PP-046</t>
+          <t>PP-059</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.3</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>Pitch Deck Review / Pitch Training</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2850,91 +2404,71 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I50" s="6">
-        <f>IF(E50="Always","Kept as in template",IF(E50="No","Omitted",IF(AND(C50="Body",H50="Reviewed"),"Notion text (no heading)",IF(C50="Body","Note: Subheader was empty.",IF(H50="Reviewed","Heading + Notion text"&amp;IF(F50="Table"," + template table",""),IF(H50="Not used","Heading"&amp;IF(F50="Table"," + template table",IF(F50="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F50="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J50" s="6" t="inlineStr"/>
+      <c r="G50" s="6">
+        <f>IF(E50="No","Omitted",IF(C50="Fixed","Kept as in template",IF(AND(C50="Body",INDEX(_notion!$C$2:$C$66,MATCH(A50,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C50="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A50,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F50="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A50,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F50="Table"," + template table",IF(F50="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F50="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>PP-047</t>
+          <t>PP-060</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.4</t>
+          <t>8.3.1</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Peer-to-Peer Learning</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I51" s="6">
-        <f>IF(E51="Always","Kept as in template",IF(E51="No","Omitted",IF(AND(C51="Body",H51="Reviewed"),"Notion text (no heading)",IF(C51="Body","Note: Subheader was empty.",IF(H51="Reviewed","Heading + Notion text"&amp;IF(F51="Table"," + template table",""),IF(H51="Not used","Heading"&amp;IF(F51="Table"," + template table",IF(F51="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F51="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J51" s="6" t="inlineStr"/>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G51" s="6">
+        <f>IF(E51="No","Omitted",IF(C51="Fixed","Kept as in template",IF(AND(C51="Body",INDEX(_notion!$C$2:$C$66,MATCH(A51,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C51="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A51,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F51="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A51,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F51="Table"," + template table",IF(F51="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F51="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>PP-048</t>
+          <t>PP-061</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.5</t>
+          <t>8.3.2</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Market Intelligence</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
+          <t>Performance and Result Reporting</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2944,44 +2478,38 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I52" s="6">
-        <f>IF(E52="Always","Kept as in template",IF(E52="No","Omitted",IF(AND(C52="Body",H52="Reviewed"),"Notion text (no heading)",IF(C52="Body","Note: Subheader was empty.",IF(H52="Reviewed","Heading + Notion text"&amp;IF(F52="Table"," + template table",""),IF(H52="Not used","Heading"&amp;IF(F52="Table"," + template table",IF(F52="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F52="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J52" s="6" t="inlineStr"/>
+      <c r="G52" s="6">
+        <f>IF(E52="No","Omitted",IF(C52="Fixed","Kept as in template",IF(AND(C52="Body",INDEX(_notion!$C$2:$C$66,MATCH(A52,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C52="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A52,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F52="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A52,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F52="Table"," + template table",IF(F52="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F52="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Not in template. From old checklist.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>PP-049</t>
+          <t>PP-062</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.6</t>
+          <t>8.3.3</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Market Briefing</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
+          <t>Final Reporting</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -2991,46 +2519,40 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I53" s="6">
-        <f>IF(E53="Always","Kept as in template",IF(E53="No","Omitted",IF(AND(C53="Body",H53="Reviewed"),"Notion text (no heading)",IF(C53="Body","Note: Subheader was empty.",IF(H53="Reviewed","Heading + Notion text"&amp;IF(F53="Table"," + template table",""),IF(H53="Not used","Heading"&amp;IF(F53="Table"," + template table",IF(F53="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F53="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J53" s="6" t="inlineStr"/>
+      <c r="G53" s="6">
+        <f>IF(E53="No","Omitted",IF(C53="Fixed","Kept as in template",IF(AND(C53="Body",INDEX(_notion!$C$2:$C$66,MATCH(A53,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C53="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A53,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F53="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A53,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F53="Table"," + template table",IF(F53="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F53="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Not in template. From old checklist.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>PP-050</t>
+          <t>PP-063</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>8.2.3.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Singapore Business Culture</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>Quality Management</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3038,31 +2560,21 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I54" s="6">
-        <f>IF(E54="Always","Kept as in template",IF(E54="No","Omitted",IF(AND(C54="Body",H54="Reviewed"),"Notion text (no heading)",IF(C54="Body","Note: Subheader was empty.",IF(H54="Reviewed","Heading + Notion text"&amp;IF(F54="Table"," + template table",""),IF(H54="Not used","Heading"&amp;IF(F54="Table"," + template table",IF(F54="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F54="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J54" s="6" t="inlineStr"/>
+      <c r="G54" s="6">
+        <f>IF(E54="No","Omitted",IF(C54="Fixed","Kept as in template",IF(AND(C54="Body",INDEX(_notion!$C$2:$C$66,MATCH(A54,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C54="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A54,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F54="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A54,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F54="Table"," + template table",IF(F54="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F54="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>PP-051</t>
+          <t>PP-064</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>8.2.4</t>
+          <t>8.4.1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -3070,157 +2582,127 @@
           <t>H3</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>Offline Components</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>KPI Monitoring and Performance</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I55" s="6">
-        <f>IF(E55="Always","Kept as in template",IF(E55="No","Omitted",IF(AND(C55="Body",H55="Reviewed"),"Notion text (no heading)",IF(C55="Body","Note: Subheader was empty.",IF(H55="Reviewed","Heading + Notion text"&amp;IF(F55="Table"," + template table",""),IF(H55="Not used","Heading"&amp;IF(F55="Table"," + template table",IF(F55="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F55="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>Parent of offline subheads.</t>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G55" s="6">
+        <f>IF(E55="No","Omitted",IF(C55="Fixed","Kept as in template",IF(AND(C55="Body",INDEX(_notion!$C$2:$C$66,MATCH(A55,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C55="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A55,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F55="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A55,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F55="Table"," + template table",IF(F55="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F55="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Template table: three KPI tiers.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>PP-052</t>
+          <t>PP-065</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>8.2.4.1</t>
+          <t>8.4.2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Networking</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Change Management and Scalability</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I56" s="6">
-        <f>IF(E56="Always","Kept as in template",IF(E56="No","Omitted",IF(AND(C56="Body",H56="Reviewed"),"Notion text (no heading)",IF(C56="Body","Note: Subheader was empty.",IF(H56="Reviewed","Heading + Notion text"&amp;IF(F56="Table"," + template table",""),IF(H56="Not used","Heading"&amp;IF(F56="Table"," + template table",IF(F56="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F56="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J56" s="6" t="inlineStr"/>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G56" s="6">
+        <f>IF(E56="No","Omitted",IF(C56="Fixed","Kept as in template",IF(AND(C56="Body",INDEX(_notion!$C$2:$C$66,MATCH(A56,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C56="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A56,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F56="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A56,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F56="Table"," + template table",IF(F56="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F56="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>PP-053</t>
+          <t>PP-066</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>8.2.4.2</t>
+          <t>8.4.3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Demo Day</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Continuity Measures</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I57" s="6">
-        <f>IF(E57="Always","Kept as in template",IF(E57="No","Omitted",IF(AND(C57="Body",H57="Reviewed"),"Notion text (no heading)",IF(C57="Body","Note: Subheader was empty.",IF(H57="Reviewed","Heading + Notion text"&amp;IF(F57="Table"," + template table",""),IF(H57="Not used","Heading"&amp;IF(F57="Table"," + template table",IF(F57="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F57="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J57" s="6" t="inlineStr"/>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G57" s="6">
+        <f>IF(E57="No","Omitted",IF(C57="Fixed","Kept as in template",IF(AND(C57="Body",INDEX(_notion!$C$2:$C$66,MATCH(A57,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C57="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A57,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F57="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A57,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F57="Table"," + template table",IF(F57="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F57="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>PP-054</t>
+          <t>PP-067</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>8.2.4.3</t>
+          <t>8.4.4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Industry Visit</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
+          <t>Sustainability Measures</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3230,1189 +2712,442 @@
           <t>None</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I58" s="6">
-        <f>IF(E58="Always","Kept as in template",IF(E58="No","Omitted",IF(AND(C58="Body",H58="Reviewed"),"Notion text (no heading)",IF(C58="Body","Note: Subheader was empty.",IF(H58="Reviewed","Heading + Notion text"&amp;IF(F58="Table"," + template table",""),IF(H58="Not used","Heading"&amp;IF(F58="Table"," + template table",IF(F58="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F58="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J58" s="6" t="inlineStr"/>
+      <c r="G58" s="6">
+        <f>IF(E58="No","Omitted",IF(C58="Fixed","Kept as in template",IF(AND(C58="Body",INDEX(_notion!$C$2:$C$66,MATCH(A58,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C58="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A58,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F58="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A58,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F58="Table"," + template table",IF(F58="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F58="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>Not in template. Notion block has no Proposal Type.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>PP-055</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>8.2.4.4</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>Regional Event Participation</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I59" s="6">
-        <f>IF(E59="Always","Kept as in template",IF(E59="No","Omitted",IF(AND(C59="Body",H59="Reviewed"),"Notion text (no heading)",IF(C59="Body","Note: Subheader was empty.",IF(H59="Reviewed","Heading + Notion text"&amp;IF(F59="Table"," + template table",""),IF(H59="Not used","Heading"&amp;IF(F59="Table"," + template table",IF(F59="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F59="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J59" s="6" t="inlineStr"/>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>PP-068</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Governance Structure and Key Personnel</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G59" s="9">
+        <f>IF(E59="No","Omitted",IF(C59="Fixed","Kept as in template",IF(AND(C59="Body",INDEX(_notion!$C$2:$C$66,MATCH(A59,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C59="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A59,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F59="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A59,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F59="Table"," + template table",IF(F59="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F59="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>PP-056</t>
+          <t>PP-069</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>8.2.4.5</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>B2B Matchmaking</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>Program Governance for Accelerator Programs</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I60" s="6">
-        <f>IF(E60="Always","Kept as in template",IF(E60="No","Omitted",IF(AND(C60="Body",H60="Reviewed"),"Notion text (no heading)",IF(C60="Body","Note: Subheader was empty.",IF(H60="Reviewed","Heading + Notion text"&amp;IF(F60="Table"," + template table",""),IF(H60="Not used","Heading"&amp;IF(F60="Table"," + template table",IF(F60="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F60="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J60" s="6" t="inlineStr"/>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="G60" s="6">
+        <f>IF(E60="No","Omitted",IF(C60="Fixed","Kept as in template",IF(AND(C60="Body",INDEX(_notion!$C$2:$C$66,MATCH(A60,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C60="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A60,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F60="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A60,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F60="Table"," + template table",IF(F60="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F60="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>PP-057</t>
+          <t>PP-070</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>8.2.4.6</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>H4</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>Investor Pitching</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>RACI Matrix</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I61" s="6">
-        <f>IF(E61="Always","Kept as in template",IF(E61="No","Omitted",IF(AND(C61="Body",H61="Reviewed"),"Notion text (no heading)",IF(C61="Body","Note: Subheader was empty.",IF(H61="Reviewed","Heading + Notion text"&amp;IF(F61="Table"," + template table",""),IF(H61="Not used","Heading"&amp;IF(F61="Table"," + template table",IF(F61="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F61="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J61" s="6" t="inlineStr"/>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G61" s="6">
+        <f>IF(E61="No","Omitted",IF(C61="Fixed","Kept as in template",IF(AND(C61="Body",INDEX(_notion!$C$2:$C$66,MATCH(A61,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C61="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A61,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F61="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A61,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F61="Table"," + template table",IF(F61="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F61="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Template repeats the RACI intro text; Notion text replaces it.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>PP-058</t>
+          <t>PP-071</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>8.2.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Open Innovation / Hackathon Management</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Start2 Group Team</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I62" s="6">
-        <f>IF(E62="Always","Kept as in template",IF(E62="No","Omitted",IF(AND(C62="Body",H62="Reviewed"),"Notion text (no heading)",IF(C62="Body","Note: Subheader was empty.",IF(H62="Reviewed","Heading + Notion text"&amp;IF(F62="Table"," + template table",""),IF(H62="Not used","Heading"&amp;IF(F62="Table"," + template table",IF(F62="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F62="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>Not in template. From old checklist.</t>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G62" s="6">
+        <f>IF(E62="No","Omitted",IF(C62="Fixed","Kept as in template",IF(AND(C62="Body",INDEX(_notion!$C$2:$C$66,MATCH(A62,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C62="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A62,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F62="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A62,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F62="Table"," + template table",IF(F62="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F62="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>Template table: team member CV card.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>PP-059</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>Reporting</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>PP-072</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Deliverables and KPIs</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I63" s="6">
-        <f>IF(E63="Always","Kept as in template",IF(E63="No","Omitted",IF(AND(C63="Body",H63="Reviewed"),"Notion text (no heading)",IF(C63="Body","Note: Subheader was empty.",IF(H63="Reviewed","Heading + Notion text"&amp;IF(F63="Table"," + template table",""),IF(H63="Not used","Heading"&amp;IF(F63="Table"," + template table",IF(F63="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F63="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J63" s="6" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G63" s="9">
+        <f>IF(E63="No","Omitted",IF(C63="Fixed","Kept as in template",IF(AND(C63="Body",INDEX(_notion!$C$2:$C$66,MATCH(A63,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C63="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A63,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F63="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A63,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F63="Table"," + template table",IF(F63="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F63="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>PP-060</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>8.3.1</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="inlineStr">
-        <is>
-          <t>Risk Management</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>PP-073</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Financial Proposal</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I64" s="6">
-        <f>IF(E64="Always","Kept as in template",IF(E64="No","Omitted",IF(AND(C64="Body",H64="Reviewed"),"Notion text (no heading)",IF(C64="Body","Note: Subheader was empty.",IF(H64="Reviewed","Heading + Notion text"&amp;IF(F64="Table"," + template table",""),IF(H64="Not used","Heading"&amp;IF(F64="Table"," + template table",IF(F64="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F64="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J64" s="6" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G64" s="9">
+        <f>IF(E64="No","Omitted",IF(C64="Fixed","Kept as in template",IF(AND(C64="Body",INDEX(_notion!$C$2:$C$66,MATCH(A64,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C64="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A64,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F64="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A64,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F64="Table"," + template table",IF(F64="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F64="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>PP-061</t>
+          <t>PP-074</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>8.3.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="inlineStr">
-        <is>
-          <t>Performance and Result Reporting</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>Price Summary</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I65" s="6">
-        <f>IF(E65="Always","Kept as in template",IF(E65="No","Omitted",IF(AND(C65="Body",H65="Reviewed"),"Notion text (no heading)",IF(C65="Body","Note: Subheader was empty.",IF(H65="Reviewed","Heading + Notion text"&amp;IF(F65="Table"," + template table",""),IF(H65="Not used","Heading"&amp;IF(F65="Table"," + template table",IF(F65="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F65="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>Not in template. From old checklist.</t>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G65" s="6">
+        <f>IF(E65="No","Omitted",IF(C65="Fixed","Kept as in template",IF(AND(C65="Body",INDEX(_notion!$C$2:$C$66,MATCH(A65,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C65="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A65,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F65="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A65,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F65="Table"," + template table",IF(F65="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F65="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Template exclusions text kept. Notion 'Indicative Costs &amp; Payment Milestone Schedule' overlaps and is not used.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>PP-062</t>
+          <t>PP-075</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>8.3.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="inlineStr">
-        <is>
-          <t>Final Reporting</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="inlineStr">
+        <is>
+          <t>Payment Schedule</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I66" s="6">
-        <f>IF(E66="Always","Kept as in template",IF(E66="No","Omitted",IF(AND(C66="Body",H66="Reviewed"),"Notion text (no heading)",IF(C66="Body","Note: Subheader was empty.",IF(H66="Reviewed","Heading + Notion text"&amp;IF(F66="Table"," + template table",""),IF(H66="Not used","Heading"&amp;IF(F66="Table"," + template table",IF(F66="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F66="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>Not in template. From old checklist.</t>
-        </is>
-      </c>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="G66" s="6">
+        <f>IF(E66="No","Omitted",IF(C66="Fixed","Kept as in template",IF(AND(C66="Body",INDEX(_notion!$C$2:$C$66,MATCH(A66,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C66="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A66,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F66="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A66,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F66="Table"," + template table",IF(F66="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F66="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>PP-063</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D67" s="14" t="inlineStr">
-        <is>
-          <t>Quality Management</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>PP-076</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Contact Details</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I67" s="6">
-        <f>IF(E67="Always","Kept as in template",IF(E67="No","Omitted",IF(AND(C67="Body",H67="Reviewed"),"Notion text (no heading)",IF(C67="Body","Note: Subheader was empty.",IF(H67="Reviewed","Heading + Notion text"&amp;IF(F67="Table"," + template table",""),IF(H67="Not used","Heading"&amp;IF(F67="Table"," + template table",IF(F67="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F67="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J67" s="6" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G67" s="9">
+        <f>IF(E67="No","Omitted",IF(C67="Fixed","Kept as in template",IF(AND(C67="Body",INDEX(_notion!$C$2:$C$66,MATCH(A67,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C67="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A67,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F67="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A67,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F67="Table"," + template table",IF(F67="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F67="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H67" s="9" t="inlineStr">
+        <is>
+          <t>Not in template. Old checklist: Point of Contact.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>PP-064</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>8.4.1</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D68" s="15" t="inlineStr">
-        <is>
-          <t>KPI Monitoring and Performance</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>PP-077</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Appendix A: Required Annexes</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Reporting &gt; Quality Management &gt; KPI Monitoring and Performance</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I68" s="6">
-        <f>IF(E68="Always","Kept as in template",IF(E68="No","Omitted",IF(AND(C68="Body",H68="Reviewed"),"Notion text (no heading)",IF(C68="Body","Note: Subheader was empty.",IF(H68="Reviewed","Heading + Notion text"&amp;IF(F68="Table"," + template table",""),IF(H68="Not used","Heading"&amp;IF(F68="Table"," + template table",IF(F68="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F68="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>Template table: three KPI tiers.</t>
-        </is>
-      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G68" s="9">
+        <f>IF(E68="No","Omitted",IF(C68="Fixed","Kept as in template",IF(AND(C68="Body",INDEX(_notion!$C$2:$C$66,MATCH(A68,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C68="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A68,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F68="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A68,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F68="Table"," + template table",IF(F68="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F68="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>PP-065</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>8.4.2</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D69" s="15" t="inlineStr">
-        <is>
-          <t>Change Management and Scalability</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>PP-078</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Appendix B: Banking Details</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>Reporting &gt; Quality Management &gt; Change Management and Scalability</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I69" s="6">
-        <f>IF(E69="Always","Kept as in template",IF(E69="No","Omitted",IF(AND(C69="Body",H69="Reviewed"),"Notion text (no heading)",IF(C69="Body","Note: Subheader was empty.",IF(H69="Reviewed","Heading + Notion text"&amp;IF(F69="Table"," + template table",""),IF(H69="Not used","Heading"&amp;IF(F69="Table"," + template table",IF(F69="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F69="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>PP-066</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>8.4.3</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D70" s="15" t="inlineStr">
-        <is>
-          <t>Continuity Measures</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="G70" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I70" s="6">
-        <f>IF(E70="Always","Kept as in template",IF(E70="No","Omitted",IF(AND(C70="Body",H70="Reviewed"),"Notion text (no heading)",IF(C70="Body","Note: Subheader was empty.",IF(H70="Reviewed","Heading + Notion text"&amp;IF(F70="Table"," + template table",""),IF(H70="Not used","Heading"&amp;IF(F70="Table"," + template table",IF(F70="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F70="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>PP-067</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>8.4.4</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="inlineStr">
-        <is>
-          <t>Sustainability Measures</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G71" s="6" t="inlineStr">
-        <is>
-          <t>Reporting &gt; Quality Management &gt; Sustainability Measures</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I71" s="6">
-        <f>IF(E71="Always","Kept as in template",IF(E71="No","Omitted",IF(AND(C71="Body",H71="Reviewed"),"Notion text (no heading)",IF(C71="Body","Note: Subheader was empty.",IF(H71="Reviewed","Heading + Notion text"&amp;IF(F71="Table"," + template table",""),IF(H71="Not used","Heading"&amp;IF(F71="Table"," + template table",IF(F71="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F71="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>Not in template. Notion block has no Proposal Type.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>PP-068</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Governance Structure and Key Personnel</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I72" s="9">
-        <f>IF(E72="Always","Kept as in template",IF(E72="No","Omitted",IF(AND(C72="Body",H72="Reviewed"),"Notion text (no heading)",IF(C72="Body","Note: Subheader was empty.",IF(H72="Reviewed","Heading + Notion text"&amp;IF(F72="Table"," + template table",""),IF(H72="Not used","Heading"&amp;IF(F72="Table"," + template table",IF(F72="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F72="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J72" s="9" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>PP-069</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Program Governance for Accelerator Programs</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Governance Structure and Key Personnel &gt; Program Governance for Accelerator Programs</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I73" s="6">
-        <f>IF(E73="Always","Kept as in template",IF(E73="No","Omitted",IF(AND(C73="Body",H73="Reviewed"),"Notion text (no heading)",IF(C73="Body","Note: Subheader was empty.",IF(H73="Reviewed","Heading + Notion text"&amp;IF(F73="Table"," + template table",""),IF(H73="Not used","Heading"&amp;IF(F73="Table"," + template table",IF(F73="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F73="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J73" s="6" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>PP-070</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>RACI Matrix</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>Governance Structure and Key Personnel &gt; RACI Matrix</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I74" s="6">
-        <f>IF(E74="Always","Kept as in template",IF(E74="No","Omitted",IF(AND(C74="Body",H74="Reviewed"),"Notion text (no heading)",IF(C74="Body","Note: Subheader was empty.",IF(H74="Reviewed","Heading + Notion text"&amp;IF(F74="Table"," + template table",""),IF(H74="Not used","Heading"&amp;IF(F74="Table"," + template table",IF(F74="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F74="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>Template repeats the RACI intro text; Notion text replaces it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
-        <is>
-          <t>PP-071</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>Start2 Group Team</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>Governance Structure and Key Personnel &gt; Start2 Group Team</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed</t>
-        </is>
-      </c>
-      <c r="I75" s="6">
-        <f>IF(E75="Always","Kept as in template",IF(E75="No","Omitted",IF(AND(C75="Body",H75="Reviewed"),"Notion text (no heading)",IF(C75="Body","Note: Subheader was empty.",IF(H75="Reviewed","Heading + Notion text"&amp;IF(F75="Table"," + template table",""),IF(H75="Not used","Heading"&amp;IF(F75="Table"," + template table",IF(F75="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F75="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>Template table: team member CV card.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>PP-072</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Deliverables and KPIs</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I76" s="9">
-        <f>IF(E76="Always","Kept as in template",IF(E76="No","Omitted",IF(AND(C76="Body",H76="Reviewed"),"Notion text (no heading)",IF(C76="Body","Note: Subheader was empty.",IF(H76="Reviewed","Heading + Notion text"&amp;IF(F76="Table"," + template table",""),IF(H76="Not used","Heading"&amp;IF(F76="Table"," + template table",IF(F76="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F76="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J76" s="9" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>PP-073</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>Financial Proposal</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I77" s="9">
-        <f>IF(E77="Always","Kept as in template",IF(E77="No","Omitted",IF(AND(C77="Body",H77="Reviewed"),"Notion text (no heading)",IF(C77="Body","Note: Subheader was empty.",IF(H77="Reviewed","Heading + Notion text"&amp;IF(F77="Table"," + template table",""),IF(H77="Not used","Heading"&amp;IF(F77="Table"," + template table",IF(F77="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F77="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J77" s="9" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>PP-074</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D78" s="14" t="inlineStr">
-        <is>
-          <t>Price Summary</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I78" s="6">
-        <f>IF(E78="Always","Kept as in template",IF(E78="No","Omitted",IF(AND(C78="Body",H78="Reviewed"),"Notion text (no heading)",IF(C78="Body","Note: Subheader was empty.",IF(H78="Reviewed","Heading + Notion text"&amp;IF(F78="Table"," + template table",""),IF(H78="Not used","Heading"&amp;IF(F78="Table"," + template table",IF(F78="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F78="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>Template exclusions text kept. Notion 'Indicative Costs &amp; Payment Milestone Schedule' overlaps and is not used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
-        <is>
-          <t>PP-075</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>Payment Schedule</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="I79" s="6">
-        <f>IF(E79="Always","Kept as in template",IF(E79="No","Omitted",IF(AND(C79="Body",H79="Reviewed"),"Notion text (no heading)",IF(C79="Body","Note: Subheader was empty.",IF(H79="Reviewed","Heading + Notion text"&amp;IF(F79="Table"," + template table",""),IF(H79="Not used","Heading"&amp;IF(F79="Table"," + template table",IF(F79="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F79="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J79" s="6" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>PP-076</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>Contact Details</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>Contact Details</t>
-        </is>
-      </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I80" s="9">
-        <f>IF(E80="Always","Kept as in template",IF(E80="No","Omitted",IF(AND(C80="Body",H80="Reviewed"),"Notion text (no heading)",IF(C80="Body","Note: Subheader was empty.",IF(H80="Reviewed","Heading + Notion text"&amp;IF(F80="Table"," + template table",""),IF(H80="Not used","Heading"&amp;IF(F80="Table"," + template table",IF(F80="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F80="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J80" s="9" t="inlineStr">
-        <is>
-          <t>Not in template. Old checklist: Point of Contact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>PP-077</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Appendix A: Required Annexes</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>No block</t>
-        </is>
-      </c>
-      <c r="I81" s="9">
-        <f>IF(E81="Always","Kept as in template",IF(E81="No","Omitted",IF(AND(C81="Body",H81="Reviewed"),"Notion text (no heading)",IF(C81="Body","Note: Subheader was empty.",IF(H81="Reviewed","Heading + Notion text"&amp;IF(F81="Table"," + template table",""),IF(H81="Not used","Heading"&amp;IF(F81="Table"," + template table",IF(F81="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F81="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>PP-078</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>Appendix B: Banking Details</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F82" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>Appendix B &gt; Banking Details</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="I82" s="9">
-        <f>IF(E82="Always","Kept as in template",IF(E82="No","Omitted",IF(AND(C82="Body",H82="Reviewed"),"Notion text (no heading)",IF(C82="Body","Note: Subheader was empty.",IF(H82="Reviewed","Heading + Notion text"&amp;IF(F82="Table"," + template table",""),IF(H82="Not used","Heading"&amp;IF(F82="Table"," + template table",IF(F82="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F82="Table"," + template table","")))))))</f>
-        <v/>
-      </c>
-      <c r="J82" s="9" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G69" s="9">
+        <f>IF(E69="No","Omitted",IF(C69="Fixed","Kept as in template",IF(AND(C69="Body",INDEX(_notion!$C$2:$C$66,MATCH(A69,_notion!$A$2:$A$66,0))="Reviewed"),"Notion text (no heading)",IF(C69="Body","Note: Subheader was empty.",IF(INDEX(_notion!$C$2:$C$66,MATCH(A69,_notion!$A$2:$A$66,0))="Reviewed","Heading + Notion text"&amp;IF(F69="Table"," + template table",""),IF(INDEX(_notion!$C$2:$C$66,MATCH(A69,_notion!$A$2:$A$66,0))="Not used","Heading"&amp;IF(F69="Table"," + template table",IF(F69="Fixed text"," + template text","")),"Heading + note: Subheader was empty."&amp;IF(F69="Table"," + template table","")))))))</f>
+        <v/>
+      </c>
+      <c r="H69" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J82"/>
-  <conditionalFormatting sqref="E5:E82">
+  <autoFilter ref="A4:H69"/>
+  <conditionalFormatting sqref="E5:E69">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>E5="Yes"</formula>
     </cfRule>
@@ -4421,7 +3156,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69 E70 E71 E72 E73 E74 E75 E76 E77 E78 E79 E80 E81 E82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Include" error="Choose Yes or No." type="list">
+    <dataValidation sqref="E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54 E55 E56 E57 E58 E59 E60 E61 E62 E63 E64 E65 E66 E67 E68 E69" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Include" error="Choose Yes or No." type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4435,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -4451,21 +3186,21 @@
     <row r="2">
       <c r="A2" s="18" t="inlineStr">
         <is>
-          <t>1. Go to the Public Partners tab. Set Include (column E) to Yes or No for each row. Only column E is edited.</t>
+          <t>1. Set Include (column E) to Yes or No. Only column E is edited.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>2. Cover Page and Table of Contents are Always included and cannot be changed.</t>
+          <t>2. Rows marked Always are part of every Public Partners proposal and cannot be switched off: Cover Page, Table of Contents, Company Information/Cover Page, Joint Submission, Executive Summary, Compliance and Eligibility, Company Overview.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>3. A subhead is only built if its parent heading is also Yes. A parent set to No removes everything under it.</t>
+          <t>3. A subhead is only built if its parent heading is also included. A parent set to No removes everything under it.</t>
         </is>
       </c>
     </row>
@@ -4482,83 +3217,1198 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Build rules (column I shows the result for each row)</t>
+          <t>Build rules (column G shows the result for each row)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>Notion Status = Reviewed: heading plus the Notion block text.</t>
+          <t>Reviewed Notion block: heading plus the Notion block text.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Notion Status = Pending Review, Empty or No block: heading plus the note 'Subheader was empty.'</t>
+          <t>Notion block Pending Review, empty, or missing: heading plus the note 'Subheader was empty.'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Notion Status = Not used: heading only, plus any template table or fixed template text.</t>
+          <t>Template tables are always kept under their heading when the row is included.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>Template tables are always kept under their heading when the row is included.</t>
+          <t>Level Body: Notion text inserted without its own heading.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Level Body: Notion text inserted without its own heading.</t>
-        </is>
-      </c>
+      <c r="A12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr"/>
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Column key</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Column key</t>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Template Content: what the Public Partners master template already holds under this heading (Table, Placeholder, Fixed text, Replaced, None). Placeholder text such as [Insert write-up here] counts as empty.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>Template Content: what the Public Partners master template already holds under this heading (Table, Placeholder, Fixed text, Replaced, None). Placeholder text such as [Insert write-up here] counts as empty.</t>
-        </is>
-      </c>
+      <c r="A15" s="18" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Notion Block: path in the Boilerplate Content Blocks database. None means no block exists.</t>
+          <t>Source: Start2_Proposal_Template_for_Public_Partners.docx heading tree and Notion Boilerplate Content Blocks, read September 2026.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Notion Block</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Notion Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PP-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PP-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PP-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Company Information</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PP-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PP-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PP-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compliance and Eligibility</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PP-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PP-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Company Overview &gt; About Start2 Group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PP-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Company Overview &gt; About Start2 Group &gt; Geographical Presence</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PP-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Company Overview &gt; Key Benefits of Partnering with Start2 Group</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PP-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PP-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in High Tech Acceleration Programs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PP-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PP-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Asia</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PP-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Europe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Empty</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Notion Status: review state of that block as of the checklist date.</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PP-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Geographies &gt; Americas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Empty</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PP-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Source: Start2_Proposal_Template_for_Public_Partners.docx heading tree and Notion Boilerplate Content Blocks, read September 2026.</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PP-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Climate Technology</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PP-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Manufacturing</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PP-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Verticals &gt; Automotive</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PP-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PP-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PP-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PP-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PP-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PP-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Technology Focus &gt; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PP-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Experience in Technology Focus &gt; Deep Tech</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PP-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Information on Network &gt; Our Mentor Network</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PP-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Information on Network &gt; Our Investor Network</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PP-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Expertise of the Firm &gt; Information on Network &gt; Our Partner Network</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PP-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PP-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Relevant Track Record &gt; Program Track Record</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PP-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Relevant Track Record &gt; Startup Success Stories</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PP-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Relevant Track Record &gt; Startup Success Stories &gt; Our Fundraising Support to Startups</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PP-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PP-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PP-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PP-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Program Structure &gt; Methodology and Frameworks for Success &gt; Program Design Strategy and Methodology</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pending Review</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PP-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Program Structure &gt; Methodology and Frameworks for Success &gt; Recruitment &amp; Selection Strategy</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PP-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PP-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PP-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PP-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PP-051</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PP-058</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PP-059</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PP-060</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PP-061</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PP-062</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PP-063</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PP-064</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Reporting &gt; Quality Management &gt; KPI Monitoring and Performance</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PP-065</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Reporting &gt; Quality Management &gt; Change Management and Scalability</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PP-066</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PP-067</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Reporting &gt; Quality Management &gt; Sustainability Measures</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PP-068</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PP-069</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Governance Structure and Key Personnel &gt; Program Governance for Accelerator Programs</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PP-070</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Governance Structure and Key Personnel &gt; RACI Matrix</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PP-071</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Governance Structure and Key Personnel &gt; Start2 Group Team</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Reviewed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PP-072</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PP-073</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PP-074</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PP-075</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PP-076</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Contact Details</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PP-077</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>No block</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PP-078</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Appendix B &gt; Banking Details</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Empty</t>
         </is>
       </c>
     </row>
